--- a/通信协议.xlsx
+++ b/通信协议.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\00_project\3_csharp\UniversalHost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E3B6EE-6793-4504-B18E-8E6164BF951C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8FB9C7-B50D-4462-AA99-4E2E488C32C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="1040" windowWidth="24130" windowHeight="12600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7770" yWindow="2290" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IAP" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="210">
   <si>
     <t>PC发送</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -93,10 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一帧字节数byte1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>第1帧</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -208,22 +204,6 @@
   </si>
   <si>
     <t>byte4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每帧字节数过大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅支持特定每帧字节数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大一帧字节数byte1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>支持的一帧字节数byte1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -868,6 +848,14 @@
   </si>
   <si>
     <t>index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一帧字节数H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一帧字节数L</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1232,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -1241,26 +1229,27 @@
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="12.9140625" customWidth="1"/>
     <col min="13" max="13" width="14.4140625" customWidth="1"/>
     <col min="14" max="14" width="7.83203125" customWidth="1"/>
     <col min="15" max="15" width="13.08203125" customWidth="1"/>
     <col min="19" max="19" width="15.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>7</v>
       </c>
@@ -1291,8 +1280,14 @@
       <c r="L3">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M3">
+        <v>9</v>
+      </c>
+      <c r="N3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>2</v>
       </c>
@@ -1300,16 +1295,16 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
         <v>9</v>
@@ -1318,7 +1313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1338,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>5</v>
@@ -1356,12 +1351,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -1373,7 +1368,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>5</v>
@@ -1382,16 +1377,22 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K6" t="s">
+        <v>208</v>
+      </c>
+      <c r="L6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M6" t="s">
         <v>9</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>12</v>
       </c>
@@ -1405,16 +1406,16 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
         <v>9</v>
@@ -1423,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>2</v>
       </c>
@@ -1431,16 +1432,16 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K9" t="s">
         <v>9</v>
@@ -1449,7 +1450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D10">
         <v>0</v>
       </c>
@@ -1507,14 +1508,8 @@
       <c r="V10">
         <v>18</v>
       </c>
-      <c r="W10">
-        <v>19</v>
-      </c>
-      <c r="X10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1531,66 +1526,60 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" t="s">
         <v>34</v>
       </c>
-      <c r="L11" t="s">
-        <v>35</v>
-      </c>
       <c r="M11" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="N11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O11" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q11" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="R11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="U11" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="V11" t="s">
-        <v>45</v>
-      </c>
-      <c r="W11" t="s">
-        <v>9</v>
-      </c>
-      <c r="X11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -1617,77 +1606,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" t="s">
-        <v>9</v>
-      </c>
-      <c r="M13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" t="s">
-        <v>9</v>
-      </c>
-      <c r="M14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>2</v>
       </c>
@@ -1695,19 +1620,19 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D16">
         <v>0</v>
       </c>
@@ -1742,49 +1667,49 @@
         <v>10</v>
       </c>
       <c r="O16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
         <v>0</v>
       </c>
       <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
         <v>17</v>
       </c>
-      <c r="D17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" t="s">
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K17" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" t="s">
         <v>34</v>
       </c>
-      <c r="L17" t="s">
-        <v>35</v>
-      </c>
       <c r="M17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" t="s">
         <v>20</v>
-      </c>
-      <c r="N17" t="s">
-        <v>21</v>
       </c>
       <c r="O17" t="s">
         <v>9</v>
@@ -1798,19 +1723,19 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
@@ -1819,13 +1744,13 @@
         <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K18" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" t="s">
         <v>34</v>
-      </c>
-      <c r="L18" t="s">
-        <v>35</v>
       </c>
       <c r="M18" t="s">
         <v>9</v>
@@ -1836,7 +1761,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -1847,16 +1772,16 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
       </c>
       <c r="I20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -1890,7 +1815,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
         <v>0</v>
@@ -1899,13 +1824,13 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
         <v>5</v>
@@ -1928,19 +1853,19 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
         <v>5</v>
@@ -1949,7 +1874,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K23" t="s">
         <v>9</v>
@@ -1960,19 +1885,19 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>5</v>
@@ -1990,24 +1915,24 @@
         <v>10</v>
       </c>
       <c r="M24" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>5</v>
@@ -2027,19 +1952,19 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H26" t="s">
         <v>5</v>
@@ -2048,7 +1973,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K26" t="s">
         <v>9</v>
@@ -2059,19 +1984,19 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H27" t="s">
         <v>5</v>
@@ -2080,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="J27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K27" t="s">
         <v>9</v>
@@ -2091,19 +2016,19 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H28" t="s">
         <v>5</v>
@@ -2112,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="J28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K28" t="s">
         <v>9</v>
@@ -2123,19 +2048,19 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H30" t="s">
         <v>5</v>
@@ -2153,24 +2078,24 @@
         <v>10</v>
       </c>
       <c r="M30" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H31" t="s">
         <v>5</v>
@@ -2190,25 +2115,25 @@
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H33" t="s">
         <v>5</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J33" t="s">
         <v>5</v>
@@ -2222,25 +2147,25 @@
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H34" t="s">
         <v>5</v>
       </c>
       <c r="I34" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J34" t="s">
         <v>5</v>
@@ -2254,25 +2179,25 @@
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
       </c>
       <c r="G35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" t="s">
         <v>63</v>
-      </c>
-      <c r="H35" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" t="s">
-        <v>68</v>
       </c>
       <c r="J35" t="s">
         <v>5</v>
@@ -2300,373 +2225,373 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" t="s">
         <v>104</v>
       </c>
-      <c r="F2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" t="s">
-        <v>109</v>
-      </c>
       <c r="I2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
         <v>71</v>
       </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" t="s">
         <v>105</v>
-      </c>
-      <c r="F3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
         <v>72</v>
       </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G26" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G27" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G28" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G29" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G30" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G31" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G32" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2688,181 +2613,181 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" t="s">
         <v>171</v>
       </c>
-      <c r="B2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D2" t="s">
-        <v>176</v>
-      </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D12" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
